--- a/static/data/exports/Retro_AS_GE_2019.xlsx
+++ b/static/data/exports/Retro_AS_GE_2019.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_GE_2019.xlsx
+++ b/static/data/exports/Retro_AS_GE_2019.xlsx
@@ -2081,11 +2081,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1720183</v>
+        <v>1720182</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ramnarayan Suklabaidya</t>
+          <t>Rabindra Chandra Das</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ramnarayan Suklabaidya</t>
+          <t>Rabindra Chandra Das</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2143,11 +2143,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1720182</v>
+        <v>1720183</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rabindra Chandra Das</t>
+          <t>Ramnarayan Suklabaidya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Rabindra Chandra Das</t>
+          <t>Ramnarayan Suklabaidya</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -17705,11 +17705,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1720434</v>
+        <v>1720435</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Anamika Sarkar</t>
+          <t>Uttam Kumar Ray</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Anamika Sarkar</t>
+          <t>Uttam Kumar Ray</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -17767,11 +17767,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1720435</v>
+        <v>1720434</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Uttam Kumar Ray</t>
+          <t>Anamika Sarkar</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Uttam Kumar Ray</t>
+          <t>Anamika Sarkar</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -23232,11 +23232,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E368" t="n">
         <v>1148</v>
@@ -23852,11 +23852,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E378" t="n">
         <v>1071</v>
@@ -24410,11 +24410,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E387" t="n">
         <v>1595</v>
@@ -25278,11 +25278,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E401" t="n">
         <v>1100</v>
@@ -26456,11 +26456,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E420" t="n">
         <v>3436</v>
@@ -32904,11 +32904,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E524" t="n">
         <v>12585</v>
@@ -33524,11 +33524,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E534" t="n">
         <v>1885</v>
@@ -41141,20 +41141,20 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>1720813</v>
+        <v>1720812</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Rubi Neog</t>
+          <t>Avijit Chakraborty</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>NRCong</t>
+          <t>BGanP</t>
         </is>
       </c>
       <c r="D657" t="n">
-        <v>19897</v>
+        <v>19867</v>
       </c>
       <c r="E657" t="n">
         <v>254</v>
@@ -41178,12 +41178,12 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Rubi Neog</t>
+          <t>Avijit Chakraborty</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>NRCong</t>
+          <t>BGanP</t>
         </is>
       </c>
       <c r="Q657" t="b">
@@ -41203,20 +41203,20 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>1720812</v>
+        <v>1720813</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Avijit Chakraborty</t>
+          <t>Rubi Neog</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>BGanP</t>
+          <t>NRCong</t>
         </is>
       </c>
       <c r="D658" t="n">
-        <v>19867</v>
+        <v>19897</v>
       </c>
       <c r="E658" t="n">
         <v>254</v>
@@ -41240,12 +41240,12 @@
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Avijit Chakraborty</t>
+          <t>Rubi Neog</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
         <is>
-          <t>BGanP</t>
+          <t>NRCong</t>
         </is>
       </c>
       <c r="Q658" t="b">
@@ -47651,20 +47651,20 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>1720918</v>
+        <v>1720917</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Mamoni Sarma</t>
+          <t>Sadek Ali</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>PUJP</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D762" t="n">
-        <v>19907</v>
+        <v>19890</v>
       </c>
       <c r="E762" t="n">
         <v>154</v>
@@ -47688,12 +47688,12 @@
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Mamoni Sarma</t>
+          <t>Sadek Ali</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>PUJP</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="Q762" t="b">
@@ -47713,20 +47713,20 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>1720917</v>
+        <v>1720918</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Sadek Ali</t>
+          <t>Mamoni Sarma</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>PUJP</t>
         </is>
       </c>
       <c r="D763" t="n">
-        <v>19890</v>
+        <v>19907</v>
       </c>
       <c r="E763" t="n">
         <v>154</v>
@@ -47750,12 +47750,12 @@
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>Sadek Ali</t>
+          <t>Mamoni Sarma</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>PUJP</t>
         </is>
       </c>
       <c r="Q763" t="b">
@@ -49892,11 +49892,11 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D798" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E798" t="n">
         <v>1659</v>
@@ -53116,11 +53116,11 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D850" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E850" t="n">
         <v>2413</v>
@@ -53922,11 +53922,11 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D863" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E863" t="n">
         <v>912</v>
@@ -73824,11 +73824,11 @@
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1184" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1184" t="n">
         <v>227</v>
@@ -80148,11 +80148,11 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1286" t="n">
         <v>431</v>
@@ -80582,11 +80582,11 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1293" t="n">
         <v>473</v>
@@ -81140,11 +81140,11 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1302" t="n">
         <v>3800</v>
@@ -81884,11 +81884,11 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1314" t="n">
         <v>3640</v>
@@ -82876,11 +82876,11 @@
       </c>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1330" t="n">
         <v>902</v>
@@ -86844,11 +86844,11 @@
       </c>
       <c r="C1394" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1394" t="n">
         <v>1235</v>
@@ -89510,11 +89510,11 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1437" t="n">
         <v>604</v>
@@ -89563,20 +89563,20 @@
     </row>
     <row r="1438">
       <c r="A1438" t="n">
-        <v>1721593</v>
+        <v>1721594</v>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>R.Anbuchezhian</t>
+          <t>Bhupen Narah</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>19894</v>
+        <v>19862</v>
       </c>
       <c r="E1438" t="n">
         <v>570</v>
@@ -89600,12 +89600,12 @@
       </c>
       <c r="K1438" t="inlineStr">
         <is>
-          <t>R.Anbuchezhian</t>
+          <t>Bhupen Narah</t>
         </is>
       </c>
       <c r="L1438" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="Q1438" t="b">
@@ -89625,20 +89625,20 @@
     </row>
     <row r="1439">
       <c r="A1439" t="n">
-        <v>1721594</v>
+        <v>1721593</v>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Bhupen Narah</t>
+          <t>R.Anbuchezhian</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>19862</v>
+        <v>19894</v>
       </c>
       <c r="E1439" t="n">
         <v>570</v>
@@ -89662,12 +89662,12 @@
       </c>
       <c r="K1439" t="inlineStr">
         <is>
-          <t>Bhupen Narah</t>
+          <t>R.Anbuchezhian</t>
         </is>
       </c>
       <c r="L1439" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="Q1439" t="b">
@@ -90068,11 +90068,11 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>19909</v>
+        <v>19875</v>
       </c>
       <c r="E1446" t="n">
         <v>1434</v>
